--- a/N100 FINANCIAL INTELLIGENCE PLATFORM/cashflow_intelligence.xlsx
+++ b/N100 FINANCIAL INTELLIGENCE PLATFORM/cashflow_intelligence.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>FCF CAGR (10Y)</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Allocation Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +536,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Aggressive Growth (Funding CapEx with Ops + External Capital)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,6 +588,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Severe Distress (Burning Ops Cash, Investing, Paying Debt - Draining Reserves)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,6 +640,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,6 +692,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,6 +744,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,6 +796,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,6 +848,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Aggressive Growth (Funding CapEx with Ops + External Capital)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -860,6 +900,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Aggressive Growth (Funding CapEx with Ops + External Capital)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -907,6 +952,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -954,6 +1004,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1001,6 +1056,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1048,6 +1108,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1095,6 +1160,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1142,6 +1212,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1189,6 +1264,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1236,6 +1316,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1283,6 +1368,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1330,6 +1420,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1377,6 +1472,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1424,6 +1524,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1471,6 +1576,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Aggressive Growth (Funding CapEx with Ops + External Capital)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1518,6 +1628,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1565,6 +1680,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1612,6 +1732,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1659,6 +1784,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1706,6 +1836,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1753,6 +1888,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1800,6 +1940,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1847,6 +1992,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1894,6 +2044,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1941,6 +2096,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1988,6 +2148,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2035,6 +2200,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Restructuring (Selling Assets to Pay Down Debt)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2082,6 +2252,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2129,6 +2304,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2176,6 +2356,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2223,6 +2408,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2270,6 +2460,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2317,6 +2512,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2364,6 +2564,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2411,6 +2616,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2458,6 +2668,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2505,6 +2720,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2552,6 +2772,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2599,6 +2824,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2646,6 +2876,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2693,6 +2928,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2740,6 +2980,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2787,6 +3032,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Distress &amp; Restructuring (Burning Ops, Selling Assets, Raising Capital to Survive)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2834,6 +3084,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2881,6 +3136,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2928,6 +3188,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Start-up / High Growth (Burning Ops Cash, Investing Heavily, Externally Funded)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2975,6 +3240,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Severe Distress (Burning Ops Cash, Investing, Paying Debt - Draining Reserves)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3022,6 +3292,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3069,6 +3344,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3116,6 +3396,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3163,6 +3448,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3210,6 +3500,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3257,6 +3552,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3304,6 +3604,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3351,6 +3656,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3398,6 +3708,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3445,6 +3760,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3492,6 +3812,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3539,6 +3864,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3586,6 +3916,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3633,6 +3968,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3680,6 +4020,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3727,6 +4072,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3774,6 +4124,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3821,6 +4176,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3868,6 +4228,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3915,6 +4280,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3962,6 +4332,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4009,6 +4384,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Aggressive Growth (Funding CapEx with Ops + External Capital)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4056,6 +4436,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4103,6 +4488,11 @@
           <t>Insufficient Data</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4148,6 +4538,11 @@
       <c r="K79" t="inlineStr">
         <is>
           <t>Insufficient Data</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Mature / Cash Cow (Reinvesting &amp; Paying Debt/Dividends)</t>
         </is>
       </c>
     </row>
